--- a/tame_output/ON/bt/strategyON_20240627.xlsx
+++ b/tame_output/ON/bt/strategyON_20240627.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>43.6%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>78.1%</t>
+          <t>78.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>45.3%</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.1%</t>
+          <t>109.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.3%</t>
+          <t>94.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>451.3%</t>
+          <t>451.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-522.1%</t>
+          <t>-522.0%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-163.8%</t>
+          <t>-163.4%</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-199.0%</t>
+          <t>-198.8%</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>61.0%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-74.3%</t>
+          <t>-74.0%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2006"/>
+  <dimension ref="A1:G2007"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47683,7 +47683,7 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729125055920937</v>
+        <v>3.729452285161986</v>
       </c>
       <c r="C2006" t="n">
         <v>3.566880009211171</v>
@@ -47699,6 +47699,29 @@
       </c>
       <c r="G2006" t="n">
         <v>3.7170363913418</v>
+      </c>
+    </row>
+    <row r="2007">
+      <c r="A2007" s="2" t="n">
+        <v>45469</v>
+      </c>
+      <c r="B2007" t="n">
+        <v>3.716502642086473</v>
+      </c>
+      <c r="C2007" t="n">
+        <v>3.569771103756472</v>
+      </c>
+      <c r="D2007" t="n">
+        <v>-3.603890889534525</v>
+      </c>
+      <c r="E2007" t="n">
+        <v>2.127858323628915</v>
+      </c>
+      <c r="F2007" t="n">
+        <v>0.2515474004239375</v>
+      </c>
+      <c r="G2007" t="n">
+        <v>3.720699544010835</v>
       </c>
     </row>
   </sheetData>
